--- a/healthcare_assessment_forms/014_surface_laboratory_assessment--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/014_surface_laboratory_assessment--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>test_results</t>
+          <t>medical_history</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Test Results</t>
+          <t>Medical History</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>test_results_table</t>
+          <t>medication_list</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Test Results Table</t>
+          <t>Medication List</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>test_results_graph</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Test Results Graph</t>
+          <t>Allergies</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>test_type_other</t>
+          <t>test_results</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Test Results</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lab_info</t>
+          <t>test_results_graph</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lab Information</t>
+          <t>Test Results Graph</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lab_test_results</t>
+          <t>test_results_table</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lab Test Results</t>
+          <t>Test Results Table</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>lab_info</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Lab Information</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>test_results_table_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Allergies</t>
+          <t>Test Results Table 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>medication_list</t>
+          <t>medical_history_notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Medication List</t>
+          <t>Medical History Notes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>medical_history_notes</t>
+          <t>test_results_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Medical History Notes</t>
+          <t>Test Results 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,159 +791,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>test_results_table</t>
+          <t>test_type_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Test Results Table</t>
+          <t>Test Type 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>test_results_graph</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Test Results Graph</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>lab_test_results</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Lab Test Results</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>patient_info_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Patient Information 2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>test_type_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Test Type 2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>test_type_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Test Type 3</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>test_type_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Test Type 4</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -960,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'blood_test'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Blood Test'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1010,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'urine_test'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Urine Test'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1027,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1044,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'blood_test'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Blood Test'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1061,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'urine_test'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Urine Test'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1078,114 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>test_type_3_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'label':_'blood_test'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'label': 'Blood Test'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>test_type_3_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'label':_'urine_test'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'label': 'Urine Test'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>test_type_3_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>test_type_4_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'label':_'blood_test'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'label': 'Blood Test'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>test_type_4_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'label':_'urine_test'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'label': 'Urine Test'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>test_type_4_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'label': 'Other'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
